--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2279124</v>
+        <v>65809277</v>
       </c>
       <c r="B2" t="n">
-        <v>96224</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219769</v>
+        <v>100572</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Mindre ekbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Cerambyx scopolii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Fuessly, 1775</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Ebbeskogsgatan., Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622681.4565245776</v>
+        <v>622596</v>
       </c>
       <c r="R2" t="n">
-        <v>6356182.944321515</v>
+        <v>6356159</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-08-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-08-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>stockupplag i blandlövsskog. Ett litet stockupplag i skogskanten mest ek men lite asp. Kom flygandes.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,33 +778,33 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>nyröjd betesmark, frisk</t>
+          <t>Ek-hasselskog med inslag av lind, asp och barr. Örtrik.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Ekstock.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3384122</v>
+        <v>2156821</v>
       </c>
       <c r="B3" t="n">
-        <v>103177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,16 +812,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,21 +830,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622626.9476048038</v>
+        <v>622629</v>
       </c>
       <c r="R3" t="n">
-        <v>6356033.31638468</v>
+        <v>6356226</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,21 +869,11 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +885,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>nyröjd betesmark, frisk</t>
+          <t>lövskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -915,19 +899,18 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2279125</v>
+        <v>2279123</v>
       </c>
       <c r="B4" t="n">
-        <v>96224</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,14 +943,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Lindresrvatet norr, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622625.4310057946</v>
+        <v>622743</v>
       </c>
       <c r="R4" t="n">
-        <v>6356011.665346754</v>
+        <v>6356252</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,21 +980,11 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,7 +996,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>nyröjd betesmark, frisk</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1037,19 +1010,18 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3787737</v>
+        <v>2279124</v>
       </c>
       <c r="B5" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221423</v>
+        <v>219769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622681.4565245776</v>
+        <v>622681</v>
       </c>
       <c r="R5" t="n">
-        <v>6356182.944321515</v>
+        <v>6356183</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,19 +1091,9 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,19 +1121,18 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3787738</v>
+        <v>2279125</v>
       </c>
       <c r="B6" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221423</v>
+        <v>219769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1208,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622597.7711119822</v>
+        <v>622625</v>
       </c>
       <c r="R6" t="n">
-        <v>6356122.105108897</v>
+        <v>6356012</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1241,21 +1202,11 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1267,7 +1218,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>ädellövskog</t>
+          <t>nyröjd betesmark, frisk</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1281,19 +1232,18 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3572246</v>
+        <v>2311109</v>
       </c>
       <c r="B7" t="n">
-        <v>96351</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221119</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Krutbrännare</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neotinea ustulata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. M. Bateman et al.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1330,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622626.9476048038</v>
+        <v>622686</v>
       </c>
       <c r="R7" t="n">
-        <v>6356033.31638468</v>
+        <v>6356197</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1363,19 +1313,9 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,54 +1343,53 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4709118</v>
+        <v>67239083</v>
       </c>
       <c r="B8" t="n">
-        <v>96925</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222295</v>
+        <v>219865</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Johannesnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Orchis militaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lindreservatet norr, Öl</t>
+          <t>Lindreservatet norrut, Öl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622681.4565245776</v>
+        <v>622559</v>
       </c>
       <c r="R8" t="n">
-        <v>6356182.944321515</v>
+        <v>6355595</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1477,22 +1416,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,33 +1435,32 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>nyröjd betesmark, frisk</t>
+          <t>fårbetad alvarlik mark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Ingela Carlström, Tommy Carlström, Stephanie Janowski</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2311109</v>
+        <v>3572246</v>
       </c>
       <c r="B9" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>221119</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Krutbrännare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neotinea ustulata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. M. Bateman et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1569,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622685.9024993429</v>
+        <v>622627</v>
       </c>
       <c r="R9" t="n">
-        <v>6356197.120603565</v>
+        <v>6356033</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1602,19 +1530,9 @@
           <t>2010-06-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2010-06-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,71 +1560,61 @@
           <t>Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>65809277</v>
+        <v>3384122</v>
       </c>
       <c r="B10" t="n">
-        <v>5141</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106155</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100572</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre ekbock</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cerambyx scopolii</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fuessly, 1775</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>slag-/vattenhåvning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ebbeskogsgatan., Öl</t>
+          <t>Lindreservatet norr, Öl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622595.5751517338</v>
+        <v>622627</v>
       </c>
       <c r="R10" t="n">
-        <v>6356159.308005731</v>
+        <v>6356033</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1730,27 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1995-08-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1995-08-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>stockupplag i blandlövsskog. Ett litet stockupplag i skogskanten mest ek men lite asp. Kom flygandes.</t>
+          <t>2010-06-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,26 +1657,464 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Ek-hasselskog med inslag av lind, asp och barr. Örtrik.</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Ekstock.</t>
+          <t>nyröjd betesmark, frisk</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Lundkvist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3787736</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lindresrvatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>622743</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6356252</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3787737</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>622681</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6356183</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>nyröjd betesmark, frisk</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3787738</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>622598</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6356122</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>ädellövskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4709118</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lindreservatet norr, Öl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>622681</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6356183</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2010-06-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>nyröjd betesmark, frisk</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45006-2025 artfynd.xlsx
+++ b/artfynd/A 45006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65809277</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2156821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2279123</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2279124</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2279125</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2311109</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67239083</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3572246</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3384122</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3787736</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1898,6 +1953,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3787737</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2009,6 +2069,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3787738</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,8 +2180,28 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4709118</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>